--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33046-2026 artfynd.xlsx
+++ b/artfynd/A 33046-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856158</v>
       </c>
       <c r="B2" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
